--- a/public/documents/pieces-defense/RF-prix-menu-demi-lune.xlsx
+++ b/public/documents/pieces-defense/RF-prix-menu-demi-lune.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Prix catalogue par periode" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Prix personnalises" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Forfaits Demi Lune (tous)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Couverture DEL hors catalogue" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +36,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +56,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2933"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +100,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,17 +469,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,21 +512,6 @@
           <t>Prix catalogue</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Qte au prix catalogue</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Qte hors catalogue</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>EUR hors catalogue</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -541,15 +537,6 @@
       <c r="E3" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1024</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -575,15 +562,6 @@
       <c r="E4" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1506</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -609,15 +587,6 @@
       <c r="E5" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -643,15 +612,6 @@
       <c r="E6" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>174</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>4993</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -676,15 +636,6 @@
       </c>
       <c r="E7" s="4" t="n">
         <v>45</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>232</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>6570</v>
       </c>
     </row>
     <row r="8">
@@ -696,23 +647,15 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>507</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>14118</v>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,0 (unique)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -794,10 +737,10 @@
         <v>19.35</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>38.7</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="7">
@@ -805,10 +748,10 @@
         <v>20</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -1951,10 +1894,10 @@
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>14118</v>
+        <v>14157</v>
       </c>
     </row>
   </sheetData>
@@ -1963,4 +1906,7812 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Heure rafale</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Nb suppressions a la carte</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Total note = somme suppr. (€)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Note n°</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>207</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>38</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>52</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>17</v>
+      </c>
+      <c r="D30" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>19</v>
+      </c>
+      <c r="D36" t="n">
+        <v>433.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>145</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>103</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>19</v>
+      </c>
+      <c r="D56" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>13</v>
+      </c>
+      <c r="D59" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>10</v>
+      </c>
+      <c r="D62" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I173"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sur les 334 Menus Demi Lune hors catalogue (annexe B), 149 sont justifies au centime par une rafale DEL (somme des lignes supprimees = total du menu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Heure note</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Note n°</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Prix unitaire menu (€)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Couverts (qte)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Total note (€)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Justifie par DEL</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Heure rafale DEL</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Somme DEL (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2022-06-12</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-08</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>187.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>108.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>186.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2022-10-29</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2022-12-15</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>82.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>194.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>90.09999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>203.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>128.8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>208.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>161.9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-09</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>102.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>433.3</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>433.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>158.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>129.7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>134.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>65.2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>182.2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr"/>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>85.90000000000001</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>320.4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>115.9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>157.3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>243.4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr"/>
+      <c r="I154" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>202.1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr"/>
+      <c r="I157" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>133.6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr"/>
+      <c r="I164" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr"/>
+      <c r="I171" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>